--- a/dados/SP_WFS.xlsx
+++ b/dados/SP_WFS.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -112,6 +112,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -189,7 +192,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_SP_WFS" displayName="Tabela_SP_WFS" ref="A1:X571" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_SP_WFS" displayName="Tabela_SP_WFS" ref="A1:X581" headerRowCount="1">
   <autoFilter ref="A1:X571"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -486,7 +489,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X571"/>
+  <dimension ref="A1:X581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -58744,6 +58747,1001 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>HT01</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>RGB(238,130,238)</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D572" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E572" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F572" s="12" t="n">
+        <v>915.015</v>
+      </c>
+      <c r="G572" s="12" t="n">
+        <v>53877.79</v>
+      </c>
+      <c r="H572" s="12" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>FYF2D66</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VALTER DA SILVA LISBOA</t>
+        </is>
+      </c>
+      <c r="K572" s="13" t="n">
+        <v>300.15</v>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:12 BRT</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V572" s="8">
+        <f>IFERROR(F572/H572,"")</f>
+        <v/>
+      </c>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>HT02</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>RGB(154,205,50)</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D573" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E573" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F573" s="12" t="n">
+        <v>640.0705</v>
+      </c>
+      <c r="G573" s="12" t="n">
+        <v>40514.66</v>
+      </c>
+      <c r="H573" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>RYV0F88</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MARCELO AMELIO DE PAULA</t>
+        </is>
+      </c>
+      <c r="K573" s="13" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:12 BRT</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V573" s="8">
+        <f>IFERROR(F573/H573,"")</f>
+        <v/>
+      </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>HT03</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>RGB(255,192,203)</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D574" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E574" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F574" s="12" t="n">
+        <v>613.5225</v>
+      </c>
+      <c r="G574" s="12" t="n">
+        <v>39000.3</v>
+      </c>
+      <c r="H574" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>RYV0F68</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JOHN WATSON SANTOS GUSMÃO</t>
+        </is>
+      </c>
+      <c r="K574" s="13" t="n">
+        <v>229.81</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:13 BRT</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V574" s="8">
+        <f>IFERROR(F574/H574,"")</f>
+        <v/>
+      </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>HT04</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>RGB(210,180,140)</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="D575" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E575" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F575" s="12" t="n">
+        <v>1669.691</v>
+      </c>
+      <c r="G575" s="12" t="n">
+        <v>110286.66</v>
+      </c>
+      <c r="H575" s="12" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>EJQ2E05</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MATEUS DA SILVA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K575" s="13" t="n">
+        <v>243.02</v>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:13 BRT</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V575" s="8">
+        <f>IFERROR(F575/H575,"")</f>
+        <v/>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>RGB(255,165,0)</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="D576" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E576" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F576" s="12" t="n">
+        <v>674.1055</v>
+      </c>
+      <c r="G576" s="12" t="n">
+        <v>44434.8</v>
+      </c>
+      <c r="H576" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>EMO9D32</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, LEANDRO RODRIGUES DOS ANJOS</t>
+        </is>
+      </c>
+      <c r="K576" s="13" t="n">
+        <v>242.01</v>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:13 BRT</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V576" s="8">
+        <f>IFERROR(F576/H576,"")</f>
+        <v/>
+      </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>HT06</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>RGB(154,205,50)</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D577" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E577" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F577" s="12" t="n">
+        <v>701.1775</v>
+      </c>
+      <c r="G577" s="12" t="n">
+        <v>46260.16</v>
+      </c>
+      <c r="H577" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>EUC5568</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, EMERSON FERREIRA</t>
+        </is>
+      </c>
+      <c r="K577" s="13" t="n">
+        <v>236.23</v>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:13 BRT</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V577" s="8">
+        <f>IFERROR(F577/H577,"")</f>
+        <v/>
+      </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>HT07</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>RGB(0,255,0)</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D578" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E578" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F578" s="12" t="n">
+        <v>710.283</v>
+      </c>
+      <c r="G578" s="12" t="n">
+        <v>25668.26</v>
+      </c>
+      <c r="H578" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>GIT0J69</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DIONE DA SILVA DANTAS</t>
+        </is>
+      </c>
+      <c r="K578" s="13" t="n">
+        <v>166.15</v>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>20/08/2026 10:13 BRT</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V578" s="8">
+        <f>IFERROR(F578/H578,"")</f>
+        <v/>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>HT11</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>RGB(255,192,203)</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>BR-DEDICADO-CAPITAL</t>
+        </is>
+      </c>
+      <c r="D579" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E579" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F579" s="12" t="n">
+        <v>606.0309999999999</v>
+      </c>
+      <c r="G579" s="12" t="n">
+        <v>42524.78</v>
+      </c>
+      <c r="H579" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>FCL5J22</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MARCIO GOMES DA COSTA</t>
+        </is>
+      </c>
+      <c r="K579" s="13" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:18 BRT</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>20/08/2026 11:04 BRT</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>MARCIO GOMES DA COSTA</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>FIORINO</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V579" s="8">
+        <f>IFERROR(F579/H579,"")</f>
+        <v/>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>HT20</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>RGB(255,255,0)</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="D580" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E580" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F580" s="12" t="n">
+        <v>236.04</v>
+      </c>
+      <c r="G580" s="12" t="n">
+        <v>63239.77</v>
+      </c>
+      <c r="H580" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>FNX2I96</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, SANDRO MARCIO FERREIRA GOMES</t>
+        </is>
+      </c>
+      <c r="K580" s="13" t="n">
+        <v>227.44</v>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:30 BRT</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>20/08/2026 14:58 BRT</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTEIRIZAÇÃO 20/08 SAIDA 21/08</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V580" s="8">
+        <f>IFERROR(F580/H580,"")</f>
+        <v/>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D581" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="E581" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="F581" s="12" t="n">
+        <v>6765.936</v>
+      </c>
+      <c r="G581" s="12" t="n">
+        <v>465807.18</v>
+      </c>
+      <c r="H581" s="12" t="n">
+        <v>17700</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K581" s="13" t="n">
+        <v>2232.12</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V581" s="8">
+        <f>IFERROR(F581/H581,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados/SP_WFS.xlsx
+++ b/dados/SP_WFS.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_SP_WFS" displayName="Tabela_SP_WFS" ref="A1:X622" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_SP_WFS" displayName="Tabela_SP_WFS" ref="A1:X629" headerRowCount="1">
   <autoFilter ref="A1:X614"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X622"/>
+  <dimension ref="A1:X629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -63959,6 +63959,709 @@
         <v/>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>HT01</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>RGB(233,150,122)</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D623" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E623" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="F623" s="12" t="n">
+        <v>1081.0955</v>
+      </c>
+      <c r="G623" s="12" t="n">
+        <v>64245.28</v>
+      </c>
+      <c r="H623" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>EJQ2E05</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MATEUS DA SILVA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K623" s="13" t="n">
+        <v>247.63</v>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>26/08/2026 07:06 BRT</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:04 BRT</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>MATEUS DA SILVA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>3/4-I</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>Parada de Atendimento</t>
+        </is>
+      </c>
+      <c r="V623" s="8">
+        <f>IFERROR(F623/H623,"")</f>
+        <v/>
+      </c>
+      <c r="W623" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X623" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>HT04</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>RGB(154,205,50)</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="D624" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E624" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F624" s="12" t="n">
+        <v>887.272</v>
+      </c>
+      <c r="G624" s="12" t="n">
+        <v>48187.11</v>
+      </c>
+      <c r="H624" s="12" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>FYF2D66</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VALTER DA SILVA LISBOA</t>
+        </is>
+      </c>
+      <c r="K624" s="13" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>26/08/2026 07:05 BRT</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:04 BRT</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>VALTER DA SILVA LISBOA</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>Parada de Atendimento</t>
+        </is>
+      </c>
+      <c r="V624" s="8">
+        <f>IFERROR(F624/H624,"")</f>
+        <v/>
+      </c>
+      <c r="W624" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X624" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>RGB(255,192,203)</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D625" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E625" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F625" s="12" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G625" s="12" t="n">
+        <v>14057.44</v>
+      </c>
+      <c r="H625" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>FNX2I96</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, SANDRO MARCIO FERREIRA GOMES</t>
+        </is>
+      </c>
+      <c r="K625" s="13" t="n">
+        <v>208.32</v>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:53 BRT</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:04 BRT</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V625" s="8">
+        <f>IFERROR(F625/H625,"")</f>
+        <v/>
+      </c>
+      <c r="W625" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>HT07</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>RGB(255,165,0)</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D626" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E626" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F626" s="12" t="n">
+        <v>1142.7728</v>
+      </c>
+      <c r="G626" s="12" t="n">
+        <v>39751.66</v>
+      </c>
+      <c r="H626" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>FMU2E05</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DEIVD MARCELO DE AMORIM</t>
+        </is>
+      </c>
+      <c r="K626" s="13" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:53 BRT</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:04 BRT</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>FIORINO</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V626" s="8">
+        <f>IFERROR(F626/H626,"")</f>
+        <v/>
+      </c>
+      <c r="W626" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X626" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>HT08</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>RGB(0,255,0)</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="D627" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E627" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F627" s="12" t="n">
+        <v>908.775</v>
+      </c>
+      <c r="G627" s="12" t="n">
+        <v>48117.44</v>
+      </c>
+      <c r="H627" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>EMO9D32</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, LEANDRO RODRIGUES DOS ANJOS</t>
+        </is>
+      </c>
+      <c r="K627" s="13" t="n">
+        <v>206.13</v>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:53 BRT</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:22 BRT</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V627" s="8">
+        <f>IFERROR(F627/H627,"")</f>
+        <v/>
+      </c>
+      <c r="W627" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X627" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>HT13</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>RGB(0,255,255)</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>BR-DEDICADO-CAPITAL</t>
+        </is>
+      </c>
+      <c r="D628" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E628" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F628" s="12" t="n">
+        <v>450.4801</v>
+      </c>
+      <c r="G628" s="12" t="n">
+        <v>25979.21</v>
+      </c>
+      <c r="H628" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>AAA0501</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RICARDO SILVA DOS ANJOS</t>
+        </is>
+      </c>
+      <c r="K628" s="13" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:53 BRT</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>25/08/2026 11:11 BRT</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>FIORINO</t>
+        </is>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V628" s="8">
+        <f>IFERROR(F628/H628,"")</f>
+        <v/>
+      </c>
+      <c r="W628" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>HT17</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>BR-CAPITAL-DEDICADO</t>
+        </is>
+      </c>
+      <c r="D629" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E629" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="F629" s="12" t="n">
+        <v>731.37</v>
+      </c>
+      <c r="G629" s="12" t="n">
+        <v>48033.48</v>
+      </c>
+      <c r="H629" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>AAA1502</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, TIAGO DE OLIVEIRA SANTOS</t>
+        </is>
+      </c>
+      <c r="K629" s="13" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:53 BRT</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>25/08/2026 12:36 BRT</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>26/08/2026 - ROTEIRIZAÇÃO 25/08 SAIDA 26/08</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V629" s="8">
+        <f>IFERROR(F629/H629,"")</f>
+        <v/>
+      </c>
+      <c r="W629" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X629" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
